--- a/pages/shp/uploads/29-09-2026 - 29-09-2026 (1).xlsx
+++ b/pages/shp/uploads/29-09-2026 - 29-09-2026 (1).xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="389">
   <si>
     <t>NOMOR AJU</t>
   </si>
@@ -347,58 +347,157 @@
     <t>FLAG PROPORSIONAL NETTO</t>
   </si>
   <si>
-    <t>000262NIW34520260929001142</t>
-  </si>
-  <si>
-    <t>262</t>
+    <t>000030NIW34520260929001513</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>050100</t>
   </si>
   <si>
     <t>050500</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>VN</t>
+  </si>
+  <si>
+    <t>088587</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>0003</t>
+  </si>
+  <si>
+    <t>09250000</t>
+  </si>
+  <si>
+    <t>IDCGK</t>
+  </si>
+  <si>
+    <t>VNSGN</t>
+  </si>
+  <si>
+    <t>2026-10-06</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
+    <t>DN</t>
+  </si>
+  <si>
     <t>BANDUNG</t>
   </si>
   <si>
-    <t>2026-09-29</t>
-  </si>
-  <si>
     <t>YUS YULIUS</t>
   </si>
   <si>
-    <t>EXIM MANAGER</t>
-  </si>
-  <si>
-    <t>IDR</t>
-  </si>
-  <si>
-    <t>031913</t>
-  </si>
-  <si>
-    <t>000262NIW34520260929001139</t>
-  </si>
-  <si>
-    <t>031908</t>
-  </si>
-  <si>
-    <t>000262NIW34520260929001141</t>
-  </si>
-  <si>
-    <t>031912</t>
-  </si>
-  <si>
-    <t>000262NIW34520260929001138</t>
-  </si>
-  <si>
-    <t>031892</t>
-  </si>
-  <si>
-    <t>000262NIW34520260929001140</t>
-  </si>
-  <si>
-    <t>031910</t>
+    <t>MANAGER EXIM</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>498306</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>000030NIW34520260929001514</t>
+  </si>
+  <si>
+    <t>09450000</t>
+  </si>
+  <si>
+    <t>498533</t>
+  </si>
+  <si>
+    <t>000030NIW34520260929001510</t>
+  </si>
+  <si>
+    <t>LK</t>
+  </si>
+  <si>
+    <t>04560000</t>
+  </si>
+  <si>
+    <t>LKCMB</t>
+  </si>
+  <si>
+    <t>497774</t>
+  </si>
+  <si>
+    <t>000030NIW34520260929001509</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>088227</t>
+  </si>
+  <si>
+    <t>0004</t>
+  </si>
+  <si>
+    <t>13640000</t>
+  </si>
+  <si>
+    <t>CNDGM</t>
+  </si>
+  <si>
+    <t>496564</t>
+  </si>
+  <si>
+    <t>000030NIW34520260929001512</t>
+  </si>
+  <si>
+    <t>MY</t>
+  </si>
+  <si>
+    <t>04190000</t>
+  </si>
+  <si>
+    <t>MYKUL</t>
+  </si>
+  <si>
+    <t>497699</t>
+  </si>
+  <si>
+    <t>000030NIW34520260929001511</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>02390000</t>
+  </si>
+  <si>
+    <t>DENUM</t>
+  </si>
+  <si>
+    <t>497804</t>
   </si>
   <si>
     <t>KODE FASILITAS TARIF</t>
@@ -413,316 +512,236 @@
     <t>NPWP BILLING</t>
   </si>
   <si>
+    <t>SERI</t>
+  </si>
+  <si>
+    <t>KODE ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE JENIS IDENTITAS</t>
+  </si>
+  <si>
+    <t>NOMOR IDENTITAS</t>
+  </si>
+  <si>
+    <t>NAMA ENTITAS</t>
+  </si>
+  <si>
+    <t>ALAMAT ENTITAS</t>
+  </si>
+  <si>
+    <t>NIB ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE JENIS API</t>
+  </si>
+  <si>
+    <t>KODE STATUS</t>
+  </si>
+  <si>
+    <t>NOMOR IJIN ENTITAS</t>
+  </si>
+  <si>
+    <t>TANGGAL IJIN ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE NEGARA</t>
+  </si>
+  <si>
+    <t>NIPER ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE KATEGORI KONSOLIDATOR</t>
+  </si>
+  <si>
+    <t>KODE AFILIASI</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
-    <t>BMP</t>
-  </si>
-  <si>
-    <t>BM</t>
-  </si>
-  <si>
-    <t>PPN</t>
-  </si>
-  <si>
-    <t>BMAD</t>
-  </si>
-  <si>
-    <t>PPH</t>
-  </si>
-  <si>
-    <t>BMTP</t>
-  </si>
-  <si>
-    <t>BMI</t>
-  </si>
-  <si>
-    <t>PPNBM</t>
-  </si>
-  <si>
-    <t>SERI</t>
-  </si>
-  <si>
-    <t>KODE ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE JENIS IDENTITAS</t>
-  </si>
-  <si>
-    <t>NOMOR IDENTITAS</t>
-  </si>
-  <si>
-    <t>NAMA ENTITAS</t>
-  </si>
-  <si>
-    <t>ALAMAT ENTITAS</t>
-  </si>
-  <si>
-    <t>NIB ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE JENIS API</t>
-  </si>
-  <si>
-    <t>KODE STATUS</t>
-  </si>
-  <si>
-    <t>NOMOR IJIN ENTITAS</t>
-  </si>
-  <si>
-    <t>TANGGAL IJIN ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE NEGARA</t>
-  </si>
-  <si>
-    <t>NIPER ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE KATEGORI KONSOLIDATOR</t>
-  </si>
-  <si>
-    <t>KODE AFILIASI</t>
+    <t>FAR EASTERN NEW APPAREL (VIETNAM) LTD</t>
+  </si>
+  <si>
+    <t>D1 STREET, BAC DONG PHU INDUSTRY PARK DONG PHU 
+DONG NAI DONG PHU COMMUNE
+ATTN: ODOM LIU</t>
+  </si>
+  <si>
+    <t>0745406926444000000000</t>
+  </si>
+  <si>
+    <t>NIRWANA ALABARE GARMENT</t>
+  </si>
+  <si>
+    <t>JL RAYA RANCAEKEK MAJALAYA NO.289 RT.002 RW.007, SOLOKANJERUK, SOLOKANJERUK, KABUPATEN BANDUNG, JAWA BARAT</t>
+  </si>
+  <si>
+    <t>0220103231143</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>0745406926444000000000</t>
-  </si>
-  <si>
-    <t>NIRWANA ALABARE GARMENT</t>
-  </si>
-  <si>
-    <t>JL RAYA RANCAEKEK MAJALAYA NO.289 RT.002 RW.007, SOLOKANJERUK, SOLOKANJERUK, KABUPATEN BANDUNG, JAWA BARAT</t>
-  </si>
-  <si>
-    <t>0220103231143</t>
+    <t>13</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>0013107743062000000000</t>
+  </si>
+  <si>
+    <t>BIROTIKA SEMESTA</t>
+  </si>
+  <si>
+    <t>MULIA BUSINESS PARK BLD F, JL MT. HARYONO KAV 58-60 RT.000 RW.000, PANCORAN, PANCORAN, KOTA ADMINISTRASI JAKARTA SELATAN, DAERAH KHUSUS IBUKOTA JAKARTA</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>LAINNYA</t>
+  </si>
+  <si>
+    <t>NO. 46, BOULEVARD TU DO, VSIP INDUSTRIAL PARK, BINH HOA WARD, HO CHI MINH CITY
+ATTN: MIRA /TINA LEE</t>
+  </si>
+  <si>
+    <t>TEEJAY LANKA</t>
+  </si>
+  <si>
+    <t>BLOCK D8-D14, SEETHAWAKA, E.P.Z
+107000 AVISSAWELLA WESTERN PROVINCE
+ATTN : HIMASHA HARRISON/ROSHAN</t>
+  </si>
+  <si>
+    <t>DONGGUAN BETTER TRIMS CO.,LTD</t>
+  </si>
+  <si>
+    <t>ROOM 1317, BUILDING 2, BEES SQUARE
+HONGYI ROAD NO1, NANCHENG DISTRICT
+,DONGGUAN CITY, GUANGDONG PROVINCE
+523078 DONGGUAN  GUANGDONG</t>
+  </si>
+  <si>
+    <t>ROOM 1317, BUILDING 2, BEES SQUARE
+HONGYI ROAD NO1, NANCHENG DISTRICT
+,DONGGUAN CITY, GUANGDONG PROVINCE
+523078 DONGGUAN  GUANGDONG
+ATTN : SOPHY LEE</t>
+  </si>
+  <si>
+    <t>B.M.O TRADISIONAL (M) SDN. BHD</t>
+  </si>
+  <si>
+    <t>JALAN CAHAYA 14 TAMAN CAHAYA SURIA 68000 AMPANG, SELANGOR DARUL EHSAN
+ATTN: NURUL</t>
+  </si>
+  <si>
+    <t>TRIUMPH INTERNATIONAL GMBH</t>
+  </si>
+  <si>
+    <t>HAUPTSTR. 80, 73540 HEUBACH
+73540 HEUBACH  BADEN-WURT</t>
+  </si>
+  <si>
+    <t>HAUPTSTR. 80, 73540 HEUBACH
+73540 HEUBACH  BADEN-WURT
+ATTN : NEUBAUER MELANIE</t>
+  </si>
+  <si>
+    <t>NOMOR DOKUMEN</t>
+  </si>
+  <si>
+    <t>TANGGAL DOKUMEN</t>
+  </si>
+  <si>
+    <t>KODE FASILITAS</t>
+  </si>
+  <si>
+    <t>KODE IJIN</t>
+  </si>
+  <si>
+    <t>920</t>
   </si>
   <si>
     <t>16/MK/WBC.09/2026</t>
   </si>
   <si>
-    <t>01-20-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>LAINNYA</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>1000000004846125000000</t>
-  </si>
-  <si>
-    <t>ARISE EMBROIDERY INDONESIA</t>
-  </si>
-  <si>
-    <t>JALAN BUYUT (KP KUTASIRIP) RT.003 RW.014, PEGAMBIRAN, LEMAHWUNGKUK, KOTA CIREBON, JAWA BARAT</t>
-  </si>
-  <si>
-    <t>08-24-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>0025445305441000000000</t>
-  </si>
-  <si>
-    <t>GUNAJAYA SANTOSA</t>
-  </si>
-  <si>
-    <t>JALAN RANCAJIGANG NO.110 RT.004 RW.010, PADAMULYA, MAJALAYA, KABUPATEN BANDUNG, JAWA BARAT</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>08-11-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>0023055023416000000000</t>
-  </si>
-  <si>
-    <t>SINAR MUTIARA</t>
-  </si>
-  <si>
-    <t>JL KENANGA GG LURAH SAADIH NO.NO. 80 RT.005 RW.001, GONDRONG, CIPONDOH, KOTA TANGERANG, BANTEN</t>
-  </si>
-  <si>
-    <t>NOMOR DOKUMEN</t>
-  </si>
-  <si>
-    <t>TANGGAL DOKUMEN</t>
-  </si>
-  <si>
-    <t>KODE FASILITAS</t>
-  </si>
-  <si>
-    <t>KODE IJIN</t>
-  </si>
-  <si>
-    <t>203</t>
-  </si>
-  <si>
-    <t>3755/TPB-SK.01/KBC.0903/2026</t>
-  </si>
-  <si>
-    <t>2026-09-15</t>
-  </si>
-  <si>
-    <t>315</t>
-  </si>
-  <si>
-    <t>251/NAG/KK/IX/2026</t>
-  </si>
-  <si>
-    <t>2026-09-11</t>
-  </si>
-  <si>
-    <t>997</t>
-  </si>
-  <si>
-    <t>CBD 2026 09 898 01 28490</t>
-  </si>
-  <si>
-    <t>994</t>
-  </si>
-  <si>
-    <t>003192/BPJ/CB/2026</t>
-  </si>
-  <si>
-    <t>261</t>
-  </si>
-  <si>
-    <t>021456</t>
-  </si>
-  <si>
-    <t>2026-09-23</t>
+    <t>2026-01-20</t>
+  </si>
+  <si>
+    <t>380</t>
+  </si>
+  <si>
+    <t>0587/E/NAG/0926</t>
+  </si>
+  <si>
+    <t>217</t>
+  </si>
+  <si>
+    <t>740</t>
+  </si>
+  <si>
+    <t>2990112263</t>
+  </si>
+  <si>
+    <t>032304</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>0588/E/NAG/0926</t>
+  </si>
+  <si>
+    <t>9642578805</t>
+  </si>
+  <si>
+    <t>035193</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>0576/E/NAK/0926</t>
+  </si>
+  <si>
+    <t>4277864161</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
   </si>
   <si>
     <t>630</t>
   </si>
   <si>
-    <t>1106/OUT/0926/01583, 1105/OUT/0926/01592, 1100/OUT/0926/01526, 1103/OUT/0926/01590, 1088/OUT/0926/01568, 1086/OUT/0926/01566, 1096/OUT/0926/01548, 1095/OUT/0926/01525</t>
-  </si>
-  <si>
-    <t>2026-09-28</t>
-  </si>
-  <si>
-    <t>1090/OUT/0926/01545, 1091/OUT/0926/01554, 1092/OUT/0926/01564, 1085/OUT/0926/01564</t>
-  </si>
-  <si>
-    <t>3284/TPB-SK.01/KBC.0903/2026</t>
-  </si>
-  <si>
-    <t>2026-08-10</t>
-  </si>
-  <si>
-    <t>224/NAG/KK/VIII/2026</t>
-  </si>
-  <si>
-    <t>2026-08-04</t>
-  </si>
-  <si>
-    <t>CBD 2026 08 898 01 22993</t>
-  </si>
-  <si>
-    <t>002756/BPJ/CB/2026</t>
-  </si>
-  <si>
-    <t>GS-06151/09/26, GS-06152/09/26, GS-06185/09/26</t>
-  </si>
-  <si>
-    <t>019552</t>
-  </si>
-  <si>
-    <t>2026-08-31</t>
-  </si>
-  <si>
-    <t>021359</t>
-  </si>
-  <si>
-    <t>2026-09-22</t>
-  </si>
-  <si>
-    <t>1104/OUT/0926/01591, 1102/OUT/0926/01589, 1101/OUT/0926/01568, 1087/OUT/0926/01549, 1094/OUT/0926/01567, 1099/OUT/0926/01556, 1097/OUT/0926/01522</t>
-  </si>
-  <si>
-    <t>1098/OUT/0926/01547, 1093/OUT/0926/01552, 1089/OUT/0926/01542</t>
-  </si>
-  <si>
-    <t>2817/TPB-SK.01/KBC.0903/2026</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>197/NAG/KK/VII/2026</t>
-  </si>
-  <si>
-    <t>2026-07-07</t>
-  </si>
-  <si>
-    <t>CBD 2026 07 898 01 18982</t>
-  </si>
-  <si>
-    <t>002380/BPJ/CB/2026</t>
-  </si>
-  <si>
-    <t>2026-07-09</t>
-  </si>
-  <si>
-    <t>GS-05933/09/26, GS-05934/09/26</t>
-  </si>
-  <si>
-    <t>016428</t>
-  </si>
-  <si>
-    <t>2026-07-21</t>
-  </si>
-  <si>
-    <t>3578/TPB-SK.01/KBC.0903/2026</t>
-  </si>
-  <si>
-    <t>2026-09-01</t>
-  </si>
-  <si>
-    <t>244/NAG/KK/VIII/2026</t>
-  </si>
-  <si>
-    <t>2026-08-27</t>
-  </si>
-  <si>
-    <t>CBD 2026 09 898 01 26866</t>
-  </si>
-  <si>
-    <t>2026-09-02</t>
-  </si>
-  <si>
-    <t>003016/BPJ/CB/2026</t>
-  </si>
-  <si>
-    <t>021261</t>
-  </si>
-  <si>
-    <t>2026-09-21</t>
-  </si>
-  <si>
-    <t>SJ260900717, SJ260900797</t>
-  </si>
-  <si>
-    <t>2026-09-24</t>
+    <t>OFC/OUT/0926/01585</t>
+  </si>
+  <si>
+    <t>0575/E/NAG/0926</t>
+  </si>
+  <si>
+    <t>6169208345</t>
+  </si>
+  <si>
+    <t>0582/E/NAG/0926</t>
+  </si>
+  <si>
+    <t>7816610992</t>
+  </si>
+  <si>
+    <t>0577/E/NAK/0926</t>
+  </si>
+  <si>
+    <t>4277904120</t>
+  </si>
+  <si>
+    <t>OFC/OUT/0926/01583</t>
   </si>
   <si>
     <t>KODE CARA ANGKUT</t>
@@ -746,27 +765,39 @@
     <t>CARA PENGANGKUTAN LAINNYA</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>K-MILE AIR</t>
+  </si>
+  <si>
+    <t>8K0801</t>
+  </si>
+  <si>
+    <t>TH</t>
+  </si>
+  <si>
+    <t>K - MILE AIR</t>
+  </si>
+  <si>
+    <t>KODE KEMASAN</t>
+  </si>
+  <si>
+    <t>JUMLAH KEMASAN</t>
+  </si>
+  <si>
+    <t>MEREK</t>
+  </si>
+  <si>
+    <t>NOMOR SEGEL</t>
+  </si>
+  <si>
+    <t>PK</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
-    <t>KODE KEMASAN</t>
-  </si>
-  <si>
-    <t>JUMLAH KEMASAN</t>
-  </si>
-  <si>
-    <t>MEREK</t>
-  </si>
-  <si>
-    <t>NOMOR SEGEL</t>
-  </si>
-  <si>
-    <t>PK</t>
-  </si>
-  <si>
-    <t>RO</t>
-  </si>
-  <si>
     <t>NOMOR KONTINER</t>
   </si>
   <si>
@@ -938,46 +969,78 @@
     <t>STATEMENT PERBEDAAN HARGA</t>
   </si>
   <si>
+    <t>61091010</t>
+  </si>
+  <si>
+    <t>FEA/0126/001</t>
+  </si>
+  <si>
+    <t>SAMPLE GARMENT AY9687 -LONG SLEEVE T-SHIRT</t>
+  </si>
+  <si>
+    <t>PCE</t>
+  </si>
+  <si>
+    <t>3204</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
     <t>62101019</t>
   </si>
   <si>
-    <t>2910</t>
-  </si>
-  <si>
-    <t>PANEL HASIL EMBROIDERRY ( KNITTED FABRIC 100% POLYESTER )</t>
-  </si>
-  <si>
-    <t>PCE</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>54071099</t>
-  </si>
-  <si>
-    <t>KN_1</t>
-  </si>
-  <si>
-    <t>FABRIC HASIL CELUP ( SINGLE JERSEY 54% COTTON 36% MODAL 10% SPANDEX )</t>
-  </si>
-  <si>
-    <t>KGM</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>54078200</t>
-  </si>
-  <si>
-    <t>KN_2</t>
-  </si>
-  <si>
-    <t>FABRIC HASIL CELUP (FABRIC 90% MODAL 10% SPANDEX  SINGLE JERSEY)</t>
-  </si>
-  <si>
-    <t>PANEL HASIL PRINTING (84% NYLON 16% SPANDEX FABRIC)</t>
+    <t>GLB/FEA/0726/002</t>
+  </si>
+  <si>
+    <t>STRIKE OFF PRINT</t>
+  </si>
+  <si>
+    <t>60063210</t>
+  </si>
+  <si>
+    <t>KN_23_KM_1</t>
+  </si>
+  <si>
+    <t>FABRIC SAMPLE 
+SINGLE JERSEY 95% MICRO MODAL 5% SPANDEX</t>
+  </si>
+  <si>
+    <t>YRD</t>
+  </si>
+  <si>
+    <t>60062200</t>
+  </si>
+  <si>
+    <t>GLB/DBT/0226/001</t>
+  </si>
+  <si>
+    <t>SWATCHES (FABRIC SAMPLE)</t>
+  </si>
+  <si>
+    <t>96071900</t>
+  </si>
+  <si>
+    <t>GLB/DBT/0926/002</t>
+  </si>
+  <si>
+    <t>SAMPLE ACCESORIES ZIPPER</t>
+  </si>
+  <si>
+    <t>39269039</t>
+  </si>
+  <si>
+    <t>SAMPLE ACCESORIES POLYBAG</t>
+  </si>
+  <si>
+    <t>SM/BMO/0926/001</t>
+  </si>
+  <si>
+    <t>GARMENT SAMPLE - SERAGAM IMIGRESEN MALAYSIA</t>
+  </si>
+  <si>
+    <t>FABRIC SAMPLE 
+FABRIC 90% MODAL 10% SPANDEX SINGLE JERSEY</t>
   </si>
   <si>
     <t>KODE PUNGUTAN</t>
@@ -1037,36 +1100,6 @@
     <t>VALUTA</t>
   </si>
   <si>
-    <t>PANEL UNTUK DI EMBROIDERRY ( KNITTED FABRIC 100% POLYESTER )</t>
-  </si>
-  <si>
-    <t>09-23-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>FABRIC UNTUK DICELUP ( SINGLE JERSEY 54% COTTON 36% MODAL 10% SPANDEX )</t>
-  </si>
-  <si>
-    <t>08-31-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>09-22-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>FABRIC UNTUK DICELUP (FABRIC 90% MODAL 10% SPANDEX  SINGLE JERSEY)</t>
-  </si>
-  <si>
-    <t>07-21-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>PANEL UNTUK DI PRINTING (84% NYLON 16% SPANDEX FABRIC)</t>
-  </si>
-  <si>
-    <t>09-21-2026 00:00:00</t>
-  </si>
-  <si>
     <t>KODE_ASAL_BAHAN_BAKU</t>
   </si>
   <si>
@@ -1094,42 +1127,12 @@
     <t>TANGGAL BPJ</t>
   </si>
   <si>
-    <t>09-15-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>JAMKRIDA JAKARTA</t>
-  </si>
-  <si>
-    <t>12-14-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>08-10-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>PT JAMKRIDA JAKARTA</t>
-  </si>
-  <si>
-    <t>11-04-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>07-08-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>10-06-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>07-09-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>09-02-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>11-29-2026 00:00:00</t>
-  </si>
-  <si>
     <t>NAMA</t>
   </si>
   <si>
+    <t>BANK BCA</t>
+  </si>
+  <si>
     <t>JENIS NILAI</t>
   </si>
   <si>
@@ -1196,22 +1199,25 @@
     <t>TANGGAL RESPON</t>
   </si>
   <si>
-    <t>26202</t>
-  </si>
-  <si>
-    <t>031892/KBC.0903/2026</t>
-  </si>
-  <si>
-    <t>031910/KBC.0903/2026</t>
-  </si>
-  <si>
-    <t>031912/KBC.0903/2026</t>
-  </si>
-  <si>
-    <t>031913/KBC.0903/2026</t>
-  </si>
-  <si>
-    <t>031908/KBC.0903/2026</t>
+    <t>3015</t>
+  </si>
+  <si>
+    <t>498273/KPU.3/2026</t>
+  </si>
+  <si>
+    <t>497452/KPU.3/2026</t>
+  </si>
+  <si>
+    <t>497557/KPU.3/2026</t>
+  </si>
+  <si>
+    <t>497527/KPU.3/2026</t>
+  </si>
+  <si>
+    <t>498052/KPU.3/2026</t>
+  </si>
+  <si>
+    <t>496318/KPU.3/2026</t>
   </si>
 </sst>
 </file>
@@ -1339,7 +1345,6 @@
     <col min="67" max="67" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="70" max="70" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="71" max="71" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="73" max="73" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="74" max="74" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="76" max="76" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="77" max="77" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -1705,23 +1710,86 @@
       <c r="C2" t="s">
         <v>106</v>
       </c>
-      <c r="M2" t="s">
+      <c r="E2" t="s">
         <v>107</v>
       </c>
+      <c r="G2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I2" t="s">
+        <v>108</v>
+      </c>
+      <c r="P2" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>110</v>
+      </c>
+      <c r="W2" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>114</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>115</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>117</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>121</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>123</v>
+      </c>
       <c r="BK2" t="n">
-        <v>0.0</v>
+        <v>0.02</v>
       </c>
       <c r="BL2" t="n">
         <v>0.0</v>
       </c>
+      <c r="BN2" t="n">
+        <v>0.0</v>
+      </c>
       <c r="BO2" t="n">
-        <v>0.0</v>
+        <v>0.02</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.0</v>
+        <v>0.65</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="BR2" t="n">
         <v>0.0</v>
@@ -1733,13 +1801,13 @@
         <v>0.0</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.327940023E7</v>
+        <v>0.0</v>
       </c>
       <c r="BV2" t="n">
         <v>0.0</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.0</v>
+        <v>17707.0</v>
       </c>
       <c r="BY2" t="n">
         <v>0.0</v>
@@ -1748,42 +1816,54 @@
         <v>0.0</v>
       </c>
       <c r="CB2" t="n">
-        <v>282.5</v>
+        <v>0.6</v>
       </c>
       <c r="CC2" t="n">
-        <v>282.2</v>
+        <v>0.6</v>
       </c>
       <c r="CD2" t="n">
         <v>0.0</v>
       </c>
       <c r="CE2" t="s">
+        <v>124</v>
+      </c>
+      <c r="CF2" t="s">
+        <v>121</v>
+      </c>
+      <c r="CG2" t="s">
+        <v>125</v>
+      </c>
+      <c r="CH2" t="s">
+        <v>126</v>
+      </c>
+      <c r="CI2" t="s">
+        <v>127</v>
+      </c>
+      <c r="CJ2" t="s">
+        <v>65</v>
+      </c>
+      <c r="CO2" t="s">
+        <v>106</v>
+      </c>
+      <c r="CP2" t="s">
+        <v>128</v>
+      </c>
+      <c r="CQ2" t="s">
+        <v>121</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CZ2" t="s">
+        <v>129</v>
+      </c>
+      <c r="DB2" t="s">
         <v>108</v>
-      </c>
-      <c r="CF2" t="s">
-        <v>109</v>
-      </c>
-      <c r="CG2" t="s">
-        <v>110</v>
-      </c>
-      <c r="CH2" t="s">
-        <v>111</v>
-      </c>
-      <c r="CI2" t="s">
-        <v>112</v>
-      </c>
-      <c r="CP2" t="s">
-        <v>113</v>
-      </c>
-      <c r="CQ2" t="s">
-        <v>109</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B3" t="s">
         <v>105</v>
@@ -1791,23 +1871,86 @@
       <c r="C3" t="s">
         <v>106</v>
       </c>
-      <c r="M3" t="s">
+      <c r="E3" t="s">
         <v>107</v>
       </c>
+      <c r="G3" t="s">
+        <v>106</v>
+      </c>
+      <c r="I3" t="s">
+        <v>108</v>
+      </c>
+      <c r="P3" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>110</v>
+      </c>
+      <c r="W3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>115</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>131</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>120</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>122</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>122</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>123</v>
+      </c>
       <c r="BK3" t="n">
-        <v>0.0</v>
+        <v>0.01</v>
       </c>
       <c r="BL3" t="n">
         <v>0.0</v>
       </c>
+      <c r="BN3" t="n">
+        <v>0.0</v>
+      </c>
       <c r="BO3" t="n">
-        <v>0.0</v>
+        <v>0.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.0</v>
+        <v>0.42</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.0</v>
+        <v>6.5</v>
       </c>
       <c r="BR3" t="n">
         <v>0.0</v>
@@ -1819,54 +1962,69 @@
         <v>0.0</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.901816232E7</v>
+        <v>0.0</v>
       </c>
       <c r="BV3" t="n">
         <v>0.0</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="BX3" t="n">
+        <v>17707.0</v>
+      </c>
+      <c r="BY3" t="n">
         <v>0.0</v>
       </c>
       <c r="CA3" t="n">
         <v>0.0</v>
       </c>
       <c r="CB3" t="n">
-        <v>806.35</v>
+        <v>0.5</v>
       </c>
       <c r="CC3" t="n">
-        <v>719.75</v>
+        <v>0.5</v>
       </c>
       <c r="CD3" t="n">
         <v>0.0</v>
       </c>
       <c r="CE3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>121</v>
+      </c>
+      <c r="CG3" t="s">
+        <v>125</v>
+      </c>
+      <c r="CH3" t="s">
+        <v>126</v>
+      </c>
+      <c r="CI3" t="s">
+        <v>127</v>
+      </c>
+      <c r="CJ3" t="s">
+        <v>65</v>
+      </c>
+      <c r="CO3" t="s">
+        <v>106</v>
+      </c>
+      <c r="CP3" t="s">
+        <v>132</v>
+      </c>
+      <c r="CQ3" t="s">
+        <v>121</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CZ3" t="s">
+        <v>129</v>
+      </c>
+      <c r="DB3" t="s">
         <v>108</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>109</v>
-      </c>
-      <c r="CG3" t="s">
-        <v>110</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>111</v>
-      </c>
-      <c r="CI3" t="s">
-        <v>112</v>
-      </c>
-      <c r="CP3" t="s">
-        <v>115</v>
-      </c>
-      <c r="CQ3" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="B4" t="s">
         <v>105</v>
@@ -1874,23 +2032,86 @@
       <c r="C4" t="s">
         <v>106</v>
       </c>
-      <c r="M4" t="s">
+      <c r="E4" t="s">
         <v>107</v>
       </c>
+      <c r="G4" t="s">
+        <v>106</v>
+      </c>
+      <c r="I4" t="s">
+        <v>108</v>
+      </c>
+      <c r="P4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>110</v>
+      </c>
+      <c r="W4" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>112</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>134</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>135</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>136</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>120</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>121</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>122</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>122</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>123</v>
+      </c>
       <c r="BK4" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="BL4" t="n">
         <v>0.0</v>
       </c>
+      <c r="BN4" t="n">
+        <v>0.0</v>
+      </c>
       <c r="BO4" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.0</v>
+        <v>1.68</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="BR4" t="n">
         <v>0.0</v>
@@ -1902,13 +2123,13 @@
         <v>0.0</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.957206717E7</v>
+        <v>0.0</v>
       </c>
       <c r="BV4" t="n">
         <v>0.0</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.0</v>
+        <v>17707.0</v>
       </c>
       <c r="BY4" t="n">
         <v>0.0</v>
@@ -1917,42 +2138,54 @@
         <v>0.0</v>
       </c>
       <c r="CB4" t="n">
-        <v>336.0</v>
+        <v>7.5</v>
       </c>
       <c r="CC4" t="n">
-        <v>335.57</v>
+        <v>7.05</v>
       </c>
       <c r="CD4" t="n">
         <v>0.0</v>
       </c>
       <c r="CE4" t="s">
+        <v>124</v>
+      </c>
+      <c r="CF4" t="s">
+        <v>121</v>
+      </c>
+      <c r="CG4" t="s">
+        <v>125</v>
+      </c>
+      <c r="CH4" t="s">
+        <v>126</v>
+      </c>
+      <c r="CI4" t="s">
+        <v>127</v>
+      </c>
+      <c r="CJ4" t="s">
+        <v>65</v>
+      </c>
+      <c r="CO4" t="s">
+        <v>106</v>
+      </c>
+      <c r="CP4" t="s">
+        <v>137</v>
+      </c>
+      <c r="CQ4" t="s">
+        <v>121</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CZ4" t="s">
+        <v>129</v>
+      </c>
+      <c r="DB4" t="s">
         <v>108</v>
-      </c>
-      <c r="CF4" t="s">
-        <v>109</v>
-      </c>
-      <c r="CG4" t="s">
-        <v>110</v>
-      </c>
-      <c r="CH4" t="s">
-        <v>111</v>
-      </c>
-      <c r="CI4" t="s">
-        <v>112</v>
-      </c>
-      <c r="CP4" t="s">
-        <v>117</v>
-      </c>
-      <c r="CQ4" t="s">
-        <v>109</v>
-      </c>
-      <c r="CT4" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="B5" t="s">
         <v>105</v>
@@ -1960,23 +2193,86 @@
       <c r="C5" t="s">
         <v>106</v>
       </c>
-      <c r="M5" t="s">
+      <c r="E5" t="s">
         <v>107</v>
       </c>
+      <c r="G5" t="s">
+        <v>106</v>
+      </c>
+      <c r="I5" t="s">
+        <v>108</v>
+      </c>
+      <c r="P5" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>110</v>
+      </c>
+      <c r="W5" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>112</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>139</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>140</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>121</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>141</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>143</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>120</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>121</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF5" t="s">
+        <v>122</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>122</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>123</v>
+      </c>
       <c r="BK5" t="n">
         <v>0.0</v>
       </c>
       <c r="BL5" t="n">
         <v>0.0</v>
       </c>
+      <c r="BN5" t="n">
+        <v>0.0</v>
+      </c>
       <c r="BO5" t="n">
         <v>0.0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.0</v>
+        <v>0.33</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.0</v>
+        <v>1.75</v>
       </c>
       <c r="BR5" t="n">
         <v>0.0</v>
@@ -1988,54 +2284,69 @@
         <v>0.0</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.384098778E8</v>
+        <v>0.0</v>
       </c>
       <c r="BV5" t="n">
         <v>0.0</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="BX5" t="n">
+        <v>17707.0</v>
+      </c>
+      <c r="BY5" t="n">
         <v>0.0</v>
       </c>
       <c r="CA5" t="n">
         <v>0.0</v>
       </c>
       <c r="CB5" t="n">
-        <v>1698.9</v>
+        <v>0.5</v>
       </c>
       <c r="CC5" t="n">
-        <v>1526.3</v>
+        <v>0.285</v>
       </c>
       <c r="CD5" t="n">
         <v>0.0</v>
       </c>
       <c r="CE5" t="s">
+        <v>124</v>
+      </c>
+      <c r="CF5" t="s">
+        <v>121</v>
+      </c>
+      <c r="CG5" t="s">
+        <v>125</v>
+      </c>
+      <c r="CH5" t="s">
+        <v>126</v>
+      </c>
+      <c r="CI5" t="s">
+        <v>127</v>
+      </c>
+      <c r="CJ5" t="s">
+        <v>65</v>
+      </c>
+      <c r="CO5" t="s">
+        <v>106</v>
+      </c>
+      <c r="CP5" t="s">
+        <v>144</v>
+      </c>
+      <c r="CQ5" t="s">
+        <v>121</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CZ5" t="s">
+        <v>129</v>
+      </c>
+      <c r="DB5" t="s">
         <v>108</v>
-      </c>
-      <c r="CF5" t="s">
-        <v>109</v>
-      </c>
-      <c r="CG5" t="s">
-        <v>110</v>
-      </c>
-      <c r="CH5" t="s">
-        <v>111</v>
-      </c>
-      <c r="CI5" t="s">
-        <v>112</v>
-      </c>
-      <c r="CP5" t="s">
-        <v>119</v>
-      </c>
-      <c r="CQ5" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="B6" t="s">
         <v>105</v>
@@ -2043,23 +2354,86 @@
       <c r="C6" t="s">
         <v>106</v>
       </c>
-      <c r="M6" t="s">
+      <c r="E6" t="s">
         <v>107</v>
       </c>
+      <c r="G6" t="s">
+        <v>106</v>
+      </c>
+      <c r="I6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P6" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>110</v>
+      </c>
+      <c r="W6" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>112</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>146</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>115</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>147</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>148</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>120</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>121</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>122</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>122</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>123</v>
+      </c>
       <c r="BK6" t="n">
-        <v>0.0</v>
+        <v>0.01</v>
       </c>
       <c r="BL6" t="n">
         <v>0.0</v>
       </c>
+      <c r="BN6" t="n">
+        <v>0.0</v>
+      </c>
       <c r="BO6" t="n">
-        <v>0.0</v>
+        <v>0.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.0</v>
+        <v>0.67</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="BR6" t="n">
         <v>0.0</v>
@@ -2071,52 +2445,225 @@
         <v>0.0</v>
       </c>
       <c r="BU6" t="n">
-        <v>3073643.74</v>
+        <v>0.0</v>
       </c>
       <c r="BV6" t="n">
         <v>0.0</v>
       </c>
       <c r="BW6" t="n">
+        <v>17707.0</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CE6" t="s">
+        <v>124</v>
+      </c>
+      <c r="CF6" t="s">
+        <v>121</v>
+      </c>
+      <c r="CG6" t="s">
+        <v>125</v>
+      </c>
+      <c r="CH6" t="s">
+        <v>126</v>
+      </c>
+      <c r="CI6" t="s">
+        <v>127</v>
+      </c>
+      <c r="CJ6" t="s">
+        <v>65</v>
+      </c>
+      <c r="CO6" t="s">
+        <v>106</v>
+      </c>
+      <c r="CP6" t="s">
+        <v>149</v>
+      </c>
+      <c r="CQ6" t="s">
+        <v>121</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CZ6" t="s">
+        <v>129</v>
+      </c>
+      <c r="DB6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E7" t="s">
+        <v>107</v>
+      </c>
+      <c r="G7" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" t="s">
+        <v>108</v>
+      </c>
+      <c r="P7" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>110</v>
+      </c>
+      <c r="W7" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>112</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>151</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>114</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>115</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>152</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>153</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>120</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>121</v>
+      </c>
+      <c r="BE7" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>122</v>
+      </c>
+      <c r="BI7" t="s">
+        <v>122</v>
+      </c>
+      <c r="BJ7" t="s">
+        <v>123</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BQ7" t="n">
         <v>1.0</v>
       </c>
-      <c r="BY6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="CC6" t="n">
-        <v>11.02</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CE6" t="s">
+      <c r="BR7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>17707.0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CE7" t="s">
+        <v>124</v>
+      </c>
+      <c r="CF7" t="s">
+        <v>121</v>
+      </c>
+      <c r="CG7" t="s">
+        <v>125</v>
+      </c>
+      <c r="CH7" t="s">
+        <v>126</v>
+      </c>
+      <c r="CI7" t="s">
+        <v>127</v>
+      </c>
+      <c r="CJ7" t="s">
+        <v>65</v>
+      </c>
+      <c r="CO7" t="s">
+        <v>106</v>
+      </c>
+      <c r="CP7" t="s">
+        <v>154</v>
+      </c>
+      <c r="CQ7" t="s">
+        <v>121</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CZ7" t="s">
+        <v>129</v>
+      </c>
+      <c r="DB7" t="s">
         <v>108</v>
-      </c>
-      <c r="CF6" t="s">
-        <v>109</v>
-      </c>
-      <c r="CG6" t="s">
-        <v>110</v>
-      </c>
-      <c r="CH6" t="s">
-        <v>111</v>
-      </c>
-      <c r="CI6" t="s">
-        <v>112</v>
-      </c>
-      <c r="CP6" t="s">
-        <v>121</v>
-      </c>
-      <c r="CQ6" t="s">
-        <v>109</v>
-      </c>
-      <c r="CT6" t="n">
-        <v>0.0</v>
       </c>
     </row>
   </sheetData>
@@ -2148,13 +2695,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -2185,10 +2732,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -2218,13 +2765,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -2258,10 +2805,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>61</v>
@@ -2273,7 +2820,7 @@
         <v>67</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -2294,13 +2841,11 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="72.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -2312,8 +2857,7 @@
     <col min="19" max="19" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="20" max="20" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -2334,64 +2878,64 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>77</v>
@@ -2406,461 +2950,52 @@
         <v>69</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>71</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>74</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>169</v>
-      </c>
-      <c r="E2" t="s">
-        <v>301</v>
-      </c>
-      <c r="F2" t="s">
         <v>302</v>
-      </c>
-      <c r="G2" t="s">
-        <v>334</v>
-      </c>
-      <c r="H2" t="s">
-        <v>237</v>
-      </c>
-      <c r="I2" t="s">
-        <v>237</v>
-      </c>
-      <c r="J2" t="s">
-        <v>237</v>
-      </c>
-      <c r="K2" t="s">
-        <v>237</v>
-      </c>
-      <c r="L2" t="s">
-        <v>304</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3665.0</v>
-      </c>
-      <c r="P2" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>106</v>
-      </c>
-      <c r="R2" t="s">
-        <v>190</v>
-      </c>
-      <c r="S2" t="s">
-        <v>335</v>
-      </c>
-      <c r="T2" t="s">
-        <v>336</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>282.2</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>3.327940023E7</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.327940023E7</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E3" t="s">
-        <v>306</v>
-      </c>
-      <c r="F3" t="s">
-        <v>307</v>
-      </c>
-      <c r="G3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H3" t="s">
-        <v>237</v>
-      </c>
-      <c r="I3" t="s">
-        <v>237</v>
-      </c>
-      <c r="J3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K3" t="s">
-        <v>237</v>
-      </c>
-      <c r="L3" t="s">
-        <v>309</v>
-      </c>
-      <c r="M3" t="n">
-        <v>719.75</v>
-      </c>
-      <c r="P3" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>106</v>
-      </c>
-      <c r="R3" t="s">
-        <v>203</v>
-      </c>
-      <c r="S3" t="s">
-        <v>338</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>719.75</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>6.901816232E7</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>6.901816232E7</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>169</v>
-      </c>
-      <c r="E4" t="s">
-        <v>301</v>
-      </c>
-      <c r="F4" t="s">
-        <v>302</v>
-      </c>
-      <c r="G4" t="s">
-        <v>334</v>
-      </c>
-      <c r="H4" t="s">
-        <v>237</v>
-      </c>
-      <c r="I4" t="s">
-        <v>237</v>
-      </c>
-      <c r="J4" t="s">
-        <v>237</v>
-      </c>
-      <c r="K4" t="s">
-        <v>237</v>
-      </c>
-      <c r="L4" t="s">
-        <v>304</v>
-      </c>
-      <c r="M4" t="n">
-        <v>4358.0</v>
-      </c>
-      <c r="P4" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>106</v>
-      </c>
-      <c r="R4" t="s">
-        <v>205</v>
-      </c>
-      <c r="S4" t="s">
-        <v>339</v>
-      </c>
-      <c r="T4" t="s">
-        <v>336</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" t="n">
-        <v>335.57</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>3.957206717E7</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.957206717E7</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>169</v>
-      </c>
-      <c r="E5" t="s">
-        <v>311</v>
-      </c>
-      <c r="F5" t="s">
-        <v>312</v>
-      </c>
-      <c r="G5" t="s">
-        <v>340</v>
-      </c>
-      <c r="H5" t="s">
-        <v>237</v>
-      </c>
-      <c r="I5" t="s">
-        <v>237</v>
-      </c>
-      <c r="J5" t="s">
-        <v>237</v>
-      </c>
-      <c r="K5" t="s">
-        <v>237</v>
-      </c>
-      <c r="L5" t="s">
-        <v>309</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1526.3</v>
-      </c>
-      <c r="P5" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>106</v>
-      </c>
-      <c r="R5" t="s">
-        <v>217</v>
-      </c>
-      <c r="S5" t="s">
-        <v>341</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1526.3</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.384098778E8</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.384098778E8</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>120</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>169</v>
-      </c>
-      <c r="E6" t="s">
-        <v>301</v>
-      </c>
-      <c r="F6" t="s">
-        <v>302</v>
-      </c>
-      <c r="G6" t="s">
-        <v>342</v>
-      </c>
-      <c r="H6" t="s">
-        <v>237</v>
-      </c>
-      <c r="I6" t="s">
-        <v>237</v>
-      </c>
-      <c r="J6" t="s">
-        <v>237</v>
-      </c>
-      <c r="K6" t="s">
-        <v>237</v>
-      </c>
-      <c r="L6" t="s">
-        <v>304</v>
-      </c>
-      <c r="M6" t="n">
-        <v>551.0</v>
-      </c>
-      <c r="P6" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>106</v>
-      </c>
-      <c r="R6" t="s">
-        <v>226</v>
-      </c>
-      <c r="S6" t="s">
-        <v>343</v>
-      </c>
-      <c r="T6" t="s">
-        <v>336</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" t="n">
-        <v>11.02</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>3073643.74</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3073643.74</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2912,76 +3047,76 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -3015,19 +3150,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -3048,7 +3183,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -3060,534 +3195,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>122</v>
+        <v>155</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D3" t="n">
-        <v>4991910.0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4951127.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C5" t="s">
-        <v>130</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B6" t="s">
-        <v>126</v>
-      </c>
-      <c r="C6" t="s">
-        <v>131</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1125256.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>104</v>
-      </c>
-      <c r="B7" t="s">
-        <v>126</v>
-      </c>
-      <c r="C7" t="s">
-        <v>132</v>
-      </c>
-      <c r="D7" t="n">
-        <v>6738936.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>104</v>
-      </c>
-      <c r="B8" t="s">
-        <v>126</v>
-      </c>
-      <c r="C8" t="s">
-        <v>133</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>104</v>
-      </c>
-      <c r="B9" t="s">
-        <v>126</v>
-      </c>
-      <c r="C9" t="s">
-        <v>134</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>114</v>
-      </c>
-      <c r="B10" t="s">
-        <v>126</v>
-      </c>
-      <c r="C10" t="s">
-        <v>132</v>
-      </c>
-      <c r="D10" t="n">
-        <v>4858275.0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>114</v>
-      </c>
-      <c r="B11" t="s">
-        <v>126</v>
-      </c>
-      <c r="C11" t="s">
-        <v>134</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>114</v>
-      </c>
-      <c r="B12" t="s">
-        <v>126</v>
-      </c>
-      <c r="C12" t="s">
-        <v>128</v>
-      </c>
-      <c r="D12" t="n">
-        <v>4843210.0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>114</v>
-      </c>
-      <c r="B13" t="s">
-        <v>126</v>
-      </c>
-      <c r="C13" t="s">
-        <v>131</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1967991.0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>114</v>
-      </c>
-      <c r="B14" t="s">
-        <v>126</v>
-      </c>
-      <c r="C14" t="s">
-        <v>133</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>114</v>
-      </c>
-      <c r="B15" t="s">
-        <v>126</v>
-      </c>
-      <c r="C15" t="s">
-        <v>127</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>114</v>
-      </c>
-      <c r="B16" t="s">
-        <v>126</v>
-      </c>
-      <c r="C16" t="s">
-        <v>129</v>
-      </c>
-      <c r="D16" t="n">
-        <v>8659161.0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>114</v>
-      </c>
-      <c r="B17" t="s">
-        <v>126</v>
-      </c>
-      <c r="C17" t="s">
-        <v>130</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>116</v>
-      </c>
-      <c r="B18" t="s">
-        <v>126</v>
-      </c>
-      <c r="C18" t="s">
-        <v>132</v>
-      </c>
-      <c r="D18" t="n">
-        <v>8013411.0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>116</v>
-      </c>
-      <c r="B19" t="s">
-        <v>126</v>
-      </c>
-      <c r="C19" t="s">
-        <v>131</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1338032.0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>116</v>
-      </c>
-      <c r="B20" t="s">
-        <v>126</v>
-      </c>
-      <c r="C20" t="s">
-        <v>130</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>116</v>
-      </c>
-      <c r="B21" t="s">
-        <v>126</v>
-      </c>
-      <c r="C21" t="s">
-        <v>129</v>
-      </c>
-      <c r="D21" t="n">
-        <v>5887341.0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>116</v>
-      </c>
-      <c r="B22" t="s">
-        <v>126</v>
-      </c>
-      <c r="C22" t="s">
-        <v>133</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>116</v>
-      </c>
-      <c r="B23" t="s">
-        <v>126</v>
-      </c>
-      <c r="C23" t="s">
-        <v>128</v>
-      </c>
-      <c r="D23" t="n">
-        <v>5935810.0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>116</v>
-      </c>
-      <c r="B24" t="s">
-        <v>126</v>
-      </c>
-      <c r="C24" t="s">
-        <v>134</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>116</v>
-      </c>
-      <c r="B25" t="s">
-        <v>126</v>
-      </c>
-      <c r="C25" t="s">
-        <v>127</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>118</v>
-      </c>
-      <c r="B26" t="s">
-        <v>126</v>
-      </c>
-      <c r="C26" t="s">
-        <v>134</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>118</v>
-      </c>
-      <c r="B27" t="s">
-        <v>126</v>
-      </c>
-      <c r="C27" t="s">
-        <v>130</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>118</v>
-      </c>
-      <c r="B28" t="s">
-        <v>126</v>
-      </c>
-      <c r="C28" t="s">
-        <v>129</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1.633443E7</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>118</v>
-      </c>
-      <c r="B29" t="s">
-        <v>126</v>
-      </c>
-      <c r="C29" t="s">
-        <v>128</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1.0084942E7</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>118</v>
-      </c>
-      <c r="B30" t="s">
-        <v>126</v>
-      </c>
-      <c r="C30" t="s">
-        <v>131</v>
-      </c>
-      <c r="D30" t="n">
-        <v>3712370.0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>120</v>
-      </c>
-      <c r="B31" t="s">
-        <v>126</v>
-      </c>
-      <c r="C31" t="s">
-        <v>129</v>
-      </c>
-      <c r="D31" t="n">
-        <v>371910.0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>120</v>
-      </c>
-      <c r="B32" t="s">
-        <v>126</v>
-      </c>
-      <c r="C32" t="s">
-        <v>132</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>120</v>
-      </c>
-      <c r="B33" t="s">
-        <v>126</v>
-      </c>
-      <c r="C33" t="s">
-        <v>130</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>120</v>
-      </c>
-      <c r="B34" t="s">
-        <v>126</v>
-      </c>
-      <c r="C34" t="s">
-        <v>131</v>
-      </c>
-      <c r="D34" t="n">
-        <v>84525.0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>120</v>
-      </c>
-      <c r="B35" t="s">
-        <v>126</v>
-      </c>
-      <c r="C35" t="s">
-        <v>128</v>
-      </c>
-      <c r="D35" t="n">
-        <v>307364.0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>120</v>
-      </c>
-      <c r="B36" t="s">
-        <v>126</v>
-      </c>
-      <c r="C36" t="s">
-        <v>134</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>120</v>
-      </c>
-      <c r="B37" t="s">
-        <v>126</v>
-      </c>
-      <c r="C37" t="s">
-        <v>127</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>120</v>
-      </c>
-      <c r="B38" t="s">
-        <v>126</v>
-      </c>
-      <c r="C38" t="s">
-        <v>133</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.0</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -3608,16 +3225,16 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="25.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3628,173 +3245,28 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E2" t="s">
-        <v>353</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.214691E9</v>
-      </c>
-      <c r="G2" t="s">
-        <v>354</v>
-      </c>
-      <c r="H2" t="s">
-        <v>355</v>
-      </c>
-      <c r="I2" t="s">
-        <v>188</v>
-      </c>
-      <c r="J2" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E3" t="s">
-        <v>356</v>
-      </c>
-      <c r="F3" t="n">
-        <v>5.70453E8</v>
-      </c>
-      <c r="G3" t="s">
         <v>357</v>
-      </c>
-      <c r="H3" t="s">
-        <v>358</v>
-      </c>
-      <c r="I3" t="s">
-        <v>201</v>
-      </c>
-      <c r="J3" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D4" t="s">
-        <v>186</v>
-      </c>
-      <c r="E4" t="s">
-        <v>353</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.214691E9</v>
-      </c>
-      <c r="G4" t="s">
-        <v>354</v>
-      </c>
-      <c r="H4" t="s">
-        <v>355</v>
-      </c>
-      <c r="I4" t="s">
-        <v>188</v>
-      </c>
-      <c r="J4" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D5" t="s">
-        <v>213</v>
-      </c>
-      <c r="E5" t="s">
-        <v>359</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4.40064E8</v>
-      </c>
-      <c r="G5" t="s">
-        <v>357</v>
-      </c>
-      <c r="H5" t="s">
-        <v>360</v>
-      </c>
-      <c r="I5" t="s">
-        <v>214</v>
-      </c>
-      <c r="J5" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C6" t="s">
-        <v>150</v>
-      </c>
-      <c r="D6" t="s">
-        <v>223</v>
-      </c>
-      <c r="E6" t="s">
-        <v>362</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.566E7</v>
-      </c>
-      <c r="G6" t="s">
-        <v>354</v>
-      </c>
-      <c r="H6" t="s">
-        <v>363</v>
-      </c>
-      <c r="I6" t="s">
-        <v>225</v>
-      </c>
-      <c r="J6" t="s">
-        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3287,8 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3823,13 +3296,97 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>364</v>
+        <v>358</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" t="s">
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -3854,8 +3411,8 @@
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="107.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="38.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="152.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -3872,49 +3429,49 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2">
@@ -3922,31 +3479,19 @@
         <v>104</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="C2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D2" t="s">
-        <v>151</v>
-      </c>
-      <c r="E2" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="F2" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="G2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H2" t="s">
-        <v>155</v>
-      </c>
-      <c r="K2" t="s">
-        <v>156</v>
-      </c>
-      <c r="L2" t="s">
-        <v>157</v>
+        <v>176</v>
+      </c>
+      <c r="M2" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="3">
@@ -3954,28 +3499,28 @@
         <v>104</v>
       </c>
       <c r="B3" t="s">
-        <v>158</v>
+        <v>122</v>
       </c>
       <c r="C3" t="s">
-        <v>158</v>
+        <v>122</v>
       </c>
       <c r="D3" t="s">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="E3" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="F3" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="G3" t="s">
-        <v>154</v>
-      </c>
-      <c r="I3" t="s">
-        <v>159</v>
+        <v>179</v>
+      </c>
+      <c r="H3" t="s">
+        <v>180</v>
       </c>
       <c r="J3" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4">
@@ -3983,412 +3528,694 @@
         <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="C4" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="D4" t="s">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="E4" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="F4" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="G4" t="s">
-        <v>164</v>
-      </c>
-      <c r="I4" t="s">
-        <v>159</v>
-      </c>
-      <c r="J4" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C5" t="s">
-        <v>158</v>
-      </c>
-      <c r="D5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E5" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="F5" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="G5" t="s">
-        <v>154</v>
-      </c>
-      <c r="I5" t="s">
-        <v>159</v>
-      </c>
-      <c r="J5" t="s">
-        <v>160</v>
-      </c>
-      <c r="L5" t="s">
-        <v>165</v>
+        <v>176</v>
+      </c>
+      <c r="M5" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s">
-        <v>150</v>
+        <v>184</v>
       </c>
       <c r="C6" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="D6" t="s">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="E6" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="F6" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="G6" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="I6" t="s">
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="J6" t="s">
-        <v>160</v>
-      </c>
-      <c r="L6" t="s">
-        <v>165</v>
+        <v>189</v>
+      </c>
+      <c r="O6" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B7" t="s">
-        <v>169</v>
+        <v>112</v>
       </c>
       <c r="C7" t="s">
-        <v>150</v>
-      </c>
-      <c r="D7" t="s">
-        <v>151</v>
-      </c>
-      <c r="E7" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="F7" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="G7" t="s">
-        <v>154</v>
-      </c>
-      <c r="H7" t="s">
-        <v>155</v>
-      </c>
-      <c r="I7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J7" t="s">
-        <v>170</v>
-      </c>
-      <c r="K7" t="s">
-        <v>156</v>
-      </c>
-      <c r="L7" t="s">
-        <v>157</v>
+        <v>190</v>
+      </c>
+      <c r="M7" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B8" t="s">
-        <v>150</v>
+        <v>182</v>
       </c>
       <c r="C8" t="s">
-        <v>150</v>
+        <v>183</v>
       </c>
       <c r="D8" t="s">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="F8" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="G8" t="s">
-        <v>154</v>
-      </c>
-      <c r="H8" t="s">
-        <v>155</v>
-      </c>
-      <c r="K8" t="s">
-        <v>156</v>
-      </c>
-      <c r="L8" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="C9" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="D9" t="s">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="F9" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="G9" t="s">
-        <v>154</v>
+        <v>187</v>
       </c>
       <c r="I9" t="s">
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="J9" t="s">
-        <v>160</v>
+        <v>189</v>
+      </c>
+      <c r="O9" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B10" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="C10" t="s">
-        <v>161</v>
-      </c>
-      <c r="D10" t="s">
-        <v>151</v>
-      </c>
-      <c r="E10" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="F10" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="G10" t="s">
-        <v>164</v>
-      </c>
-      <c r="I10" t="s">
-        <v>159</v>
-      </c>
-      <c r="J10" t="s">
-        <v>160</v>
+        <v>190</v>
+      </c>
+      <c r="M10" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="B11" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="C11" t="s">
-        <v>158</v>
+        <v>122</v>
       </c>
       <c r="D11" t="s">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="F11" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="G11" t="s">
-        <v>154</v>
-      </c>
-      <c r="I11" t="s">
-        <v>159</v>
+        <v>179</v>
+      </c>
+      <c r="H11" t="s">
+        <v>180</v>
       </c>
       <c r="J11" t="s">
-        <v>160</v>
-      </c>
-      <c r="L11" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="B12" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="C12" t="s">
-        <v>150</v>
+        <v>184</v>
       </c>
       <c r="D12" t="s">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="F12" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="G12" t="s">
-        <v>154</v>
-      </c>
-      <c r="H12" t="s">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="I12" t="s">
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="J12" t="s">
-        <v>170</v>
-      </c>
-      <c r="K12" t="s">
-        <v>156</v>
-      </c>
-      <c r="L12" t="s">
-        <v>157</v>
+        <v>189</v>
+      </c>
+      <c r="O12" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="B13" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="C13" t="s">
-        <v>161</v>
-      </c>
-      <c r="D13" t="s">
-        <v>151</v>
-      </c>
-      <c r="E13" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="F13" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="G13" t="s">
-        <v>168</v>
-      </c>
-      <c r="I13" t="s">
-        <v>159</v>
-      </c>
-      <c r="J13" t="s">
-        <v>160</v>
-      </c>
-      <c r="L13" t="s">
-        <v>171</v>
+        <v>192</v>
+      </c>
+      <c r="M13" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="B14" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="C14" t="s">
-        <v>150</v>
-      </c>
-      <c r="D14" t="s">
-        <v>151</v>
-      </c>
-      <c r="E14" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="F14" t="s">
-        <v>153</v>
+        <v>191</v>
       </c>
       <c r="G14" t="s">
-        <v>154</v>
-      </c>
-      <c r="H14" t="s">
-        <v>155</v>
-      </c>
-      <c r="K14" t="s">
-        <v>156</v>
-      </c>
-      <c r="L14" t="s">
-        <v>157</v>
+        <v>192</v>
+      </c>
+      <c r="M14" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="B15" t="s">
-        <v>158</v>
+        <v>122</v>
       </c>
       <c r="C15" t="s">
-        <v>158</v>
+        <v>122</v>
       </c>
       <c r="D15" t="s">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="E15" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="F15" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="G15" t="s">
-        <v>154</v>
-      </c>
-      <c r="I15" t="s">
-        <v>159</v>
+        <v>179</v>
+      </c>
+      <c r="H15" t="s">
+        <v>180</v>
       </c>
       <c r="J15" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="B16" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="C16" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="D16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" t="s">
+        <v>177</v>
+      </c>
+      <c r="F16" t="s">
+        <v>178</v>
+      </c>
+      <c r="G16" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>138</v>
+      </c>
+      <c r="B17" t="s">
+        <v>184</v>
+      </c>
+      <c r="C17" t="s">
+        <v>184</v>
+      </c>
+      <c r="D17" t="s">
+        <v>112</v>
+      </c>
+      <c r="E17" t="s">
+        <v>185</v>
+      </c>
+      <c r="F17" t="s">
+        <v>186</v>
+      </c>
+      <c r="G17" t="s">
+        <v>187</v>
+      </c>
+      <c r="I17" t="s">
+        <v>188</v>
+      </c>
+      <c r="J17" t="s">
+        <v>189</v>
+      </c>
+      <c r="O17" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>138</v>
+      </c>
+      <c r="B18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C18" t="s">
+        <v>112</v>
+      </c>
+      <c r="F18" t="s">
+        <v>193</v>
+      </c>
+      <c r="G18" t="s">
+        <v>194</v>
+      </c>
+      <c r="M18" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>138</v>
+      </c>
+      <c r="B19" t="s">
+        <v>174</v>
+      </c>
+      <c r="C19" t="s">
+        <v>174</v>
+      </c>
+      <c r="F19" t="s">
+        <v>193</v>
+      </c>
+      <c r="G19" t="s">
+        <v>195</v>
+      </c>
+      <c r="M19" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20" t="s">
+        <v>122</v>
+      </c>
+      <c r="C20" t="s">
+        <v>122</v>
+      </c>
+      <c r="D20" t="s">
+        <v>112</v>
+      </c>
+      <c r="E20" t="s">
+        <v>177</v>
+      </c>
+      <c r="F20" t="s">
+        <v>178</v>
+      </c>
+      <c r="G20" t="s">
+        <v>179</v>
+      </c>
+      <c r="H20" t="s">
+        <v>180</v>
+      </c>
+      <c r="J20" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>138</v>
+      </c>
+      <c r="B21" t="s">
+        <v>182</v>
+      </c>
+      <c r="C21" t="s">
+        <v>183</v>
+      </c>
+      <c r="D21" t="s">
+        <v>112</v>
+      </c>
+      <c r="E21" t="s">
+        <v>177</v>
+      </c>
+      <c r="F21" t="s">
+        <v>178</v>
+      </c>
+      <c r="G21" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>145</v>
+      </c>
+      <c r="B22" t="s">
+        <v>174</v>
+      </c>
+      <c r="C22" t="s">
+        <v>174</v>
+      </c>
+      <c r="F22" t="s">
+        <v>196</v>
+      </c>
+      <c r="G22" t="s">
+        <v>197</v>
+      </c>
+      <c r="M22" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>145</v>
+      </c>
+      <c r="B23" t="s">
+        <v>122</v>
+      </c>
+      <c r="C23" t="s">
+        <v>122</v>
+      </c>
+      <c r="D23" t="s">
+        <v>112</v>
+      </c>
+      <c r="E23" t="s">
+        <v>177</v>
+      </c>
+      <c r="F23" t="s">
+        <v>178</v>
+      </c>
+      <c r="G23" t="s">
+        <v>179</v>
+      </c>
+      <c r="H23" t="s">
+        <v>180</v>
+      </c>
+      <c r="J23" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>145</v>
+      </c>
+      <c r="B24" t="s">
+        <v>182</v>
+      </c>
+      <c r="C24" t="s">
+        <v>183</v>
+      </c>
+      <c r="D24" t="s">
+        <v>112</v>
+      </c>
+      <c r="E24" t="s">
+        <v>177</v>
+      </c>
+      <c r="F24" t="s">
+        <v>178</v>
+      </c>
+      <c r="G24" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>145</v>
+      </c>
+      <c r="B25" t="s">
+        <v>112</v>
+      </c>
+      <c r="C25" t="s">
+        <v>112</v>
+      </c>
+      <c r="F25" t="s">
+        <v>196</v>
+      </c>
+      <c r="G25" t="s">
+        <v>197</v>
+      </c>
+      <c r="M25" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>145</v>
+      </c>
+      <c r="B26" t="s">
+        <v>184</v>
+      </c>
+      <c r="C26" t="s">
+        <v>184</v>
+      </c>
+      <c r="D26" t="s">
+        <v>112</v>
+      </c>
+      <c r="E26" t="s">
+        <v>185</v>
+      </c>
+      <c r="F26" t="s">
+        <v>186</v>
+      </c>
+      <c r="G26" t="s">
+        <v>187</v>
+      </c>
+      <c r="I26" t="s">
+        <v>188</v>
+      </c>
+      <c r="J26" t="s">
+        <v>189</v>
+      </c>
+      <c r="O26" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>150</v>
+      </c>
+      <c r="B27" t="s">
+        <v>184</v>
+      </c>
+      <c r="C27" t="s">
+        <v>184</v>
+      </c>
+      <c r="D27" t="s">
+        <v>112</v>
+      </c>
+      <c r="E27" t="s">
+        <v>185</v>
+      </c>
+      <c r="F27" t="s">
+        <v>186</v>
+      </c>
+      <c r="G27" t="s">
+        <v>187</v>
+      </c>
+      <c r="I27" t="s">
+        <v>188</v>
+      </c>
+      <c r="J27" t="s">
+        <v>189</v>
+      </c>
+      <c r="O27" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>150</v>
+      </c>
+      <c r="B28" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28" t="s">
+        <v>112</v>
+      </c>
+      <c r="F28" t="s">
+        <v>198</v>
+      </c>
+      <c r="G28" t="s">
+        <v>199</v>
+      </c>
+      <c r="M28" t="s">
         <v>151</v>
       </c>
-      <c r="E16" t="s">
-        <v>172</v>
-      </c>
-      <c r="F16" t="s">
-        <v>173</v>
-      </c>
-      <c r="G16" t="s">
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>150</v>
+      </c>
+      <c r="B29" t="s">
         <v>174</v>
       </c>
-      <c r="I16" t="s">
-        <v>159</v>
-      </c>
-      <c r="J16" t="s">
-        <v>160</v>
+      <c r="C29" t="s">
+        <v>174</v>
+      </c>
+      <c r="F29" t="s">
+        <v>198</v>
+      </c>
+      <c r="G29" t="s">
+        <v>200</v>
+      </c>
+      <c r="M29" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>150</v>
+      </c>
+      <c r="B30" t="s">
+        <v>122</v>
+      </c>
+      <c r="C30" t="s">
+        <v>122</v>
+      </c>
+      <c r="D30" t="s">
+        <v>112</v>
+      </c>
+      <c r="E30" t="s">
+        <v>177</v>
+      </c>
+      <c r="F30" t="s">
+        <v>178</v>
+      </c>
+      <c r="G30" t="s">
+        <v>179</v>
+      </c>
+      <c r="H30" t="s">
+        <v>180</v>
+      </c>
+      <c r="J30" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>150</v>
+      </c>
+      <c r="B31" t="s">
+        <v>182</v>
+      </c>
+      <c r="C31" t="s">
+        <v>183</v>
+      </c>
+      <c r="D31" t="s">
+        <v>112</v>
+      </c>
+      <c r="E31" t="s">
+        <v>177</v>
+      </c>
+      <c r="F31" t="s">
+        <v>178</v>
+      </c>
+      <c r="G31" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -4411,12 +4238,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -4439,7 +4266,7 @@
   <cols>
     <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -4448,83 +4275,97 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="C1" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="D1" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="B2" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C2" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="B3" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C3" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="B4" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C4" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="B5" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C5" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s">
+        <v>382</v>
+      </c>
+      <c r="C6" t="s">
         <v>387</v>
       </c>
-      <c r="C6" t="s">
-        <v>392</v>
-      </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>138</v>
+      </c>
+      <c r="B7" t="s">
+        <v>382</v>
+      </c>
+      <c r="C7" t="s">
+        <v>388</v>
+      </c>
+      <c r="D7" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -4547,7 +4388,7 @@
   <cols>
     <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="167.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -4558,22 +4399,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2">
@@ -4584,13 +4425,13 @@
         <v>1.0</v>
       </c>
       <c r="C2" t="s">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="D2" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="E2" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3">
@@ -4601,13 +4442,13 @@
         <v>2.0</v>
       </c>
       <c r="C3" t="s">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="D3" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="E3" t="s">
-        <v>184</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4">
@@ -4618,13 +4459,13 @@
         <v>3.0</v>
       </c>
       <c r="C4" t="s">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="D4" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="E4" t="s">
-        <v>181</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5">
@@ -4635,13 +4476,13 @@
         <v>4.0</v>
       </c>
       <c r="C5" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="D5" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="E5" t="s">
-        <v>181</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6">
@@ -4652,472 +4493,404 @@
         <v>5.0</v>
       </c>
       <c r="C6" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D6" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="E6" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="B7" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="C7" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="D7" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="E7" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="B8" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="C8" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="D8" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="E8" t="s">
-        <v>194</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B9" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="C9" t="s">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="D9" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="E9" t="s">
-        <v>197</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B10" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="C10" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="D10" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="E10" t="s">
-        <v>199</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B11" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="C11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D11" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="E11" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="B12" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="C12" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="D12" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="E12" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="B13" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="C13" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="D13" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="E13" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="B14" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="C14" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="D14" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="E14" t="s">
-        <v>204</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="B15" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="C15" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="D15" t="s">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="E15" t="s">
-        <v>181</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="B16" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="C16" t="s">
-        <v>182</v>
+        <v>222</v>
       </c>
       <c r="D16" t="s">
-        <v>183</v>
+        <v>223</v>
       </c>
       <c r="E16" t="s">
-        <v>184</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B17" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C17" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="D17" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="E17" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B18" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="C18" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="D18" t="s">
-        <v>188</v>
+        <v>224</v>
       </c>
       <c r="E18" t="s">
-        <v>181</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B19" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="C19" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="D19" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="E19" t="s">
-        <v>206</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B20" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="C20" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="D20" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="E20" t="s">
-        <v>194</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="B21" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="C21" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="D21" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E21" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B22" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="C22" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="D22" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="E22" t="s">
-        <v>210</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B23" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="C23" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="D23" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="E23" t="s">
-        <v>212</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B24" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="C24" t="s">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="D24" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="E24" t="s">
-        <v>210</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="B25" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="C25" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="D25" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E25" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="B26" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="C26" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="D26" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="E26" t="s">
-        <v>194</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="B27" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="C27" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="D27" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E27" t="s">
-        <v>218</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="B28" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="C28" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="D28" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="E28" t="s">
-        <v>220</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="B29" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="C29" t="s">
-        <v>182</v>
+        <v>222</v>
       </c>
       <c r="D29" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="E29" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>120</v>
-      </c>
-      <c r="B30" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="C30" t="s">
-        <v>185</v>
-      </c>
-      <c r="D30" t="s">
-        <v>223</v>
-      </c>
-      <c r="E30" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>120</v>
-      </c>
-      <c r="B31" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="C31" t="s">
-        <v>187</v>
-      </c>
-      <c r="D31" t="s">
-        <v>225</v>
-      </c>
-      <c r="E31" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>120</v>
-      </c>
-      <c r="B32" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="C32" t="s">
-        <v>189</v>
-      </c>
-      <c r="D32" t="s">
-        <v>226</v>
-      </c>
-      <c r="E32" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>120</v>
-      </c>
-      <c r="B33" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="C33" t="s">
-        <v>192</v>
-      </c>
-      <c r="D33" t="s">
-        <v>228</v>
-      </c>
-      <c r="E33" t="s">
-        <v>229</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -5153,28 +4926,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2">
@@ -5185,63 +4958,116 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>150</v>
+        <v>238</v>
+      </c>
+      <c r="D2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F2" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>150</v>
+        <v>238</v>
       </c>
       <c r="D3" t="s">
-        <v>160</v>
+        <v>239</v>
       </c>
       <c r="E3" t="s">
-        <v>237</v>
+        <v>240</v>
+      </c>
+      <c r="F3" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>150</v>
+        <v>238</v>
+      </c>
+      <c r="D4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F4" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>150</v>
+        <v>238</v>
       </c>
       <c r="D5" t="s">
-        <v>160</v>
+        <v>242</v>
       </c>
       <c r="E5" t="s">
-        <v>237</v>
+        <v>240</v>
+      </c>
+      <c r="F5" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="s">
+        <v>238</v>
+      </c>
+      <c r="D6" t="s">
+        <v>239</v>
+      </c>
+      <c r="E6" t="s">
+        <v>240</v>
+      </c>
+      <c r="F6" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
         <v>150</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D7" t="s">
+        <v>242</v>
+      </c>
+      <c r="E7" t="s">
+        <v>240</v>
+      </c>
+      <c r="F7" t="s">
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -5273,19 +5099,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2">
@@ -5296,72 +5122,98 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D3" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D5" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -5395,22 +5247,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -5452,61 +5304,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>375</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>60</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>376</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -5530,8 +5382,8 @@
     <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="70.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="58.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -5546,8 +5398,7 @@
     <col min="23" max="23" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="32" max="32" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="34" max="34" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -5594,58 +5445,58 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>77</v>
@@ -5657,19 +5508,19 @@
         <v>78</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>69</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>71</v>
@@ -5684,25 +5535,25 @@
         <v>64</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="AM1" s="1" t="s">
         <v>61</v>
@@ -5711,94 +5562,94 @@
         <v>74</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="AS1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="AU1" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="BO1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2">
@@ -5809,52 +5660,52 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="D2" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E2" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="F2" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="G2" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="H2" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="I2" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="J2" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="K2" t="n">
-        <v>3665.0</v>
+        <v>2.0</v>
       </c>
       <c r="L2" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="M2" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="T2" t="n">
-        <v>282.2</v>
+        <v>0.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.327940023E7</v>
+        <v>0.0</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.327940023E7</v>
+        <v>0.0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.0</v>
+        <v>17707.0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="AF2" t="n">
         <v>0.0</v>
@@ -5868,6 +5719,9 @@
       <c r="AI2" t="n">
         <v>0.0</v>
       </c>
+      <c r="AJ2" t="n">
+        <v>5.0</v>
+      </c>
       <c r="AK2" t="n">
         <v>0.0</v>
       </c>
@@ -5877,67 +5731,76 @@
       <c r="AN2" t="n">
         <v>0.0</v>
       </c>
+      <c r="AS2" t="s">
+        <v>310</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>311</v>
+      </c>
       <c r="BJ2" t="n">
         <v>0.0</v>
       </c>
+      <c r="BO2" t="s">
+        <v>108</v>
+      </c>
       <c r="BR2" t="s">
-        <v>305</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="D3" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="E3" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="F3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="G3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="H3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="I3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="J3" t="s">
         <v>309</v>
       </c>
       <c r="K3" t="n">
-        <v>719.75</v>
+        <v>13.0</v>
       </c>
       <c r="L3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="M3" t="n">
-        <v>30.0</v>
+        <v>1.0</v>
       </c>
       <c r="T3" t="n">
-        <v>719.75</v>
+        <v>0.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.901816232E7</v>
+        <v>0.0</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.901816232E7</v>
+        <v>0.0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.0</v>
+        <v>17707.0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.0</v>
+        <v>6.5</v>
       </c>
       <c r="AF3" t="n">
         <v>0.0</v>
@@ -5951,6 +5814,9 @@
       <c r="AI3" t="n">
         <v>0.0</v>
       </c>
+      <c r="AJ3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AK3" t="n">
         <v>0.0</v>
       </c>
@@ -5960,83 +5826,92 @@
       <c r="AN3" t="n">
         <v>0.0</v>
       </c>
+      <c r="AS3" t="s">
+        <v>310</v>
+      </c>
       <c r="AY3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="BJ3" t="n">
         <v>0.0</v>
       </c>
+      <c r="BO3" t="s">
+        <v>108</v>
+      </c>
       <c r="BR3" t="s">
-        <v>305</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D4" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E4" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="F4" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="G4" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="H4" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="I4" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="J4" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="K4" t="n">
-        <v>4358.0</v>
+        <v>20.0</v>
       </c>
       <c r="L4" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="M4" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="T4" t="n">
-        <v>335.57</v>
+        <v>7.05</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.957206717E7</v>
+        <v>0.0</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.957206717E7</v>
+        <v>0.0</v>
       </c>
       <c r="AB4" t="n">
+        <v>17707.0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>1.0</v>
       </c>
-      <c r="AC4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0.0</v>
-      </c>
       <c r="AK4" t="n">
         <v>0.0</v>
       </c>
@@ -6046,67 +5921,76 @@
       <c r="AN4" t="n">
         <v>0.0</v>
       </c>
+      <c r="AS4" t="s">
+        <v>310</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>311</v>
+      </c>
       <c r="BJ4" t="n">
         <v>0.0</v>
       </c>
+      <c r="BO4" t="s">
+        <v>108</v>
+      </c>
       <c r="BR4" t="s">
-        <v>305</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="D5" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="E5" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="F5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="G5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="H5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="I5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="J5" t="s">
         <v>309</v>
       </c>
       <c r="K5" t="n">
-        <v>1526.3</v>
+        <v>3.0</v>
       </c>
       <c r="L5" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="M5" t="n">
-        <v>61.0</v>
+        <v>0.0</v>
       </c>
       <c r="T5" t="n">
-        <v>1526.3</v>
+        <v>0.171</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.384098778E8</v>
+        <v>0.0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.384098778E8</v>
+        <v>0.0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.0</v>
+        <v>17707.0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.0</v>
+        <v>0.75</v>
       </c>
       <c r="AF5" t="n">
         <v>0.0</v>
@@ -6120,6 +6004,9 @@
       <c r="AI5" t="n">
         <v>0.0</v>
       </c>
+      <c r="AJ5" t="n">
+        <v>0.25</v>
+      </c>
       <c r="AK5" t="n">
         <v>0.0</v>
       </c>
@@ -6129,97 +6016,400 @@
       <c r="AN5" t="n">
         <v>0.0</v>
       </c>
+      <c r="AS5" t="s">
+        <v>310</v>
+      </c>
       <c r="AY5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="BJ5" t="n">
         <v>0.0</v>
       </c>
+      <c r="BO5" t="s">
+        <v>108</v>
+      </c>
       <c r="BR5" t="s">
-        <v>305</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>322</v>
+      </c>
+      <c r="D6" t="s">
+        <v>323</v>
+      </c>
+      <c r="E6" t="s">
+        <v>324</v>
+      </c>
+      <c r="F6" t="s">
+        <v>248</v>
+      </c>
+      <c r="G6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H6" t="s">
+        <v>248</v>
+      </c>
+      <c r="I6" t="s">
+        <v>248</v>
+      </c>
+      <c r="J6" t="s">
+        <v>309</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L6" t="s">
+        <v>247</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>17707.0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>310</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>311</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO6" t="s">
+        <v>108</v>
+      </c>
+      <c r="BR6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>138</v>
+      </c>
+      <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="s">
-        <v>301</v>
-      </c>
-      <c r="D6" t="s">
-        <v>302</v>
-      </c>
-      <c r="E6" t="s">
-        <v>314</v>
-      </c>
-      <c r="F6" t="s">
-        <v>237</v>
-      </c>
-      <c r="G6" t="s">
-        <v>237</v>
-      </c>
-      <c r="H6" t="s">
-        <v>237</v>
-      </c>
-      <c r="I6" t="s">
-        <v>237</v>
-      </c>
-      <c r="J6" t="s">
-        <v>304</v>
-      </c>
-      <c r="K6" t="n">
-        <v>551.0</v>
-      </c>
-      <c r="L6" t="s">
-        <v>242</v>
-      </c>
-      <c r="M6" t="n">
+      <c r="C7" t="s">
+        <v>325</v>
+      </c>
+      <c r="D7" t="s">
+        <v>323</v>
+      </c>
+      <c r="E7" t="s">
+        <v>326</v>
+      </c>
+      <c r="F7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G7" t="s">
+        <v>248</v>
+      </c>
+      <c r="H7" t="s">
+        <v>248</v>
+      </c>
+      <c r="I7" t="s">
+        <v>248</v>
+      </c>
+      <c r="J7" t="s">
+        <v>309</v>
+      </c>
+      <c r="K7" t="n">
         <v>1.0</v>
       </c>
-      <c r="T6" t="n">
-        <v>11.02</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3073643.74</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3073643.74</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="L7" t="s">
+        <v>247</v>
+      </c>
+      <c r="M7" t="n">
         <v>1.0</v>
       </c>
-      <c r="AC6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BR6" t="s">
-        <v>305</v>
+      <c r="T7" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>17707.0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>310</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>311</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO7" t="s">
+        <v>108</v>
+      </c>
+      <c r="BR7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>306</v>
+      </c>
+      <c r="D8" t="s">
+        <v>327</v>
+      </c>
+      <c r="E8" t="s">
+        <v>328</v>
+      </c>
+      <c r="F8" t="s">
+        <v>248</v>
+      </c>
+      <c r="G8" t="s">
+        <v>248</v>
+      </c>
+      <c r="H8" t="s">
+        <v>248</v>
+      </c>
+      <c r="I8" t="s">
+        <v>248</v>
+      </c>
+      <c r="J8" t="s">
+        <v>309</v>
+      </c>
+      <c r="K8" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="L8" t="s">
+        <v>247</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>17707.0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>310</v>
+      </c>
+      <c r="AY8" t="s">
+        <v>311</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO8" t="s">
+        <v>108</v>
+      </c>
+      <c r="BR8" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>315</v>
+      </c>
+      <c r="D9" t="s">
+        <v>248</v>
+      </c>
+      <c r="E9" t="s">
+        <v>329</v>
+      </c>
+      <c r="F9" t="s">
+        <v>248</v>
+      </c>
+      <c r="G9" t="s">
+        <v>248</v>
+      </c>
+      <c r="H9" t="s">
+        <v>248</v>
+      </c>
+      <c r="I9" t="s">
+        <v>248</v>
+      </c>
+      <c r="J9" t="s">
+        <v>318</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L9" t="s">
+        <v>247</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>17707.0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>310</v>
+      </c>
+      <c r="AY9" t="s">
+        <v>311</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO9" t="s">
+        <v>108</v>
+      </c>
+      <c r="BR9" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -6265,58 +6455,58 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
